--- a/mmm_engine/data/dt_smb_weekly_dummy.xlsx
+++ b/mmm_engine/data/dt_smb_weekly_dummy.xlsx
@@ -22,25 +22,25 @@
     <t>cv</t>
   </si>
   <si>
-    <t>META_s</t>
+    <t>Meta_s</t>
   </si>
   <si>
-    <t>GOOGLE_SEARCH_s</t>
+    <t>Google_Search_s</t>
   </si>
   <si>
-    <t>LINE_s</t>
+    <t>Line_s</t>
   </si>
   <si>
-    <t>SEO_s</t>
+    <t>Seo_s</t>
   </si>
   <si>
-    <t>YAHOO_s</t>
+    <t>Yahoo_s</t>
   </si>
   <si>
-    <t>YOUTUBE_s</t>
+    <t>YouTube_s</t>
   </si>
   <si>
-    <t>CAMPAIGN_s</t>
+    <t>Campaign_s</t>
   </si>
 </sst>
 </file>
